--- a/database/event/4553/event_4553_evp_summary.xlsx
+++ b/database/event/4553/event_4553_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.824</v>
+        <v>10.3889</v>
       </c>
       <c r="C2" t="n">
-        <v>5.1716</v>
+        <v>5.469</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5473</v>
+        <v>3.695</v>
       </c>
       <c r="E2" t="n">
-        <v>9.824</v>
+        <v>10.3889</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4233</v>
+        <v>3.9882</v>
       </c>
       <c r="G2" t="n">
         <v>6.4007</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4233</v>
+        <v>3.9882</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4233</v>
+        <v>3.9882</v>
       </c>
       <c r="J2" t="n">
         <v>6.4007</v>
@@ -529,7 +529,7 @@
         <v>250</v>
       </c>
       <c r="M2" t="n">
-        <v>9.824</v>
+        <v>10.3889</v>
       </c>
       <c r="N2" t="n">
         <v>407</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1914</v>
+        <v>7.1616</v>
       </c>
       <c r="C3" t="n">
-        <v>3.7858</v>
+        <v>3.7701</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4838</v>
+        <v>2.4093</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1914</v>
+        <v>7.1616</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1448</v>
+        <v>4.115</v>
       </c>
       <c r="G3" t="n">
         <v>3.0466</v>
       </c>
       <c r="H3" t="n">
-        <v>4.196</v>
+        <v>4.1493</v>
       </c>
       <c r="I3" t="n">
         <v>4.2549</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.113</v>
+        <v>6.072</v>
       </c>
       <c r="C4" t="n">
-        <v>3.2181</v>
+        <v>3.1965</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0482</v>
+        <v>1.9752</v>
       </c>
       <c r="E4" t="n">
-        <v>6.113</v>
+        <v>6.072</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6729</v>
+        <v>3.6319</v>
       </c>
       <c r="G4" t="n">
         <v>2.4401</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6729</v>
+        <v>3.6319</v>
       </c>
       <c r="I4" t="n">
         <v>3.7244</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1868</v>
+        <v>5.1604</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7305</v>
+        <v>2.7166</v>
       </c>
       <c r="D5" t="n">
-        <v>1.674</v>
+        <v>1.612</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1868</v>
+        <v>5.1604</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3666</v>
+        <v>2.3402</v>
       </c>
       <c r="G5" t="n">
         <v>2.8202</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3666</v>
+        <v>2.3402</v>
       </c>
       <c r="I5" t="n">
         <v>2.3998</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.883</v>
+        <v>4.998</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5706</v>
+        <v>2.6311</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5513</v>
+        <v>1.5473</v>
       </c>
       <c r="E6" t="n">
-        <v>4.883</v>
+        <v>4.998</v>
       </c>
       <c r="F6" t="n">
-        <v>4.7513</v>
+        <v>4.8663</v>
       </c>
       <c r="G6" t="n">
         <v>0.1317</v>
       </c>
       <c r="H6" t="n">
-        <v>6.555</v>
+        <v>7.0507</v>
       </c>
       <c r="I6" t="n">
-        <v>5.313</v>
+        <v>5.7148</v>
       </c>
       <c r="J6" t="n">
         <v>0.1317</v>
@@ -713,7 +713,7 @@
         <v>73</v>
       </c>
       <c r="M6" t="n">
-        <v>5.4447</v>
+        <v>5.846500000000001</v>
       </c>
       <c r="N6" t="n">
         <v>205</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6351</v>
+        <v>4.5994</v>
       </c>
       <c r="C7" t="n">
-        <v>2.44</v>
+        <v>2.4213</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4511</v>
+        <v>1.3885</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6351</v>
+        <v>4.5994</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2395</v>
+        <v>3.2038</v>
       </c>
       <c r="G7" t="n">
         <v>1.3956</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2395</v>
+        <v>3.2038</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2849</v>
+        <v>3.2854</v>
       </c>
       <c r="J7" t="n">
         <v>1.3956</v>
@@ -759,7 +759,7 @@
         <v>87</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6805</v>
+        <v>4.681</v>
       </c>
       <c r="N7" t="n">
         <v>301</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.2487</v>
+        <v>4.2618</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2366</v>
+        <v>2.2435</v>
       </c>
       <c r="D8" t="n">
-        <v>1.295</v>
+        <v>1.254</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2487</v>
+        <v>4.2618</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4443</v>
+        <v>4.5013</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1956</v>
+        <v>-0.2395</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6656</v>
+        <v>5.5493</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7311</v>
+        <v>4.4978</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1956</v>
+        <v>-0.2395</v>
       </c>
       <c r="K8" t="n">
-        <v>214</v>
+        <v>129</v>
       </c>
       <c r="L8" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5355</v>
+        <v>4.2583</v>
       </c>
       <c r="N8" t="n">
-        <v>301</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.2106</v>
+        <v>4.2155</v>
       </c>
       <c r="C9" t="n">
-        <v>2.2166</v>
+        <v>2.2192</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2796</v>
+        <v>1.2355</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2106</v>
+        <v>4.2155</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4501</v>
+        <v>4.4111</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2395</v>
+        <v>-0.1956</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3431</v>
+        <v>4.6136</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3307</v>
+        <v>4.7311</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2395</v>
+        <v>-0.1956</v>
       </c>
       <c r="K9" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
       <c r="L9" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="M9" t="n">
-        <v>4.091200000000001</v>
+        <v>4.5355</v>
       </c>
       <c r="N9" t="n">
-        <v>198</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9038</v>
+        <v>4.0245</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0551</v>
+        <v>2.1186</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1557</v>
+        <v>1.1595</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9038</v>
+        <v>4.0245</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2247</v>
+        <v>3.3454</v>
       </c>
       <c r="G10" t="n">
         <v>0.6791</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2247</v>
+        <v>3.3454</v>
       </c>
       <c r="I10" t="n">
-        <v>2.6137</v>
+        <v>2.7115</v>
       </c>
       <c r="J10" t="n">
         <v>0.6791</v>
@@ -897,7 +897,7 @@
         <v>69</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2928</v>
+        <v>3.3906</v>
       </c>
       <c r="N10" t="n">
         <v>198</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.7185</v>
+        <v>3.7046</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9575</v>
+        <v>1.9502</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0808</v>
+        <v>1.032</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7185</v>
+        <v>3.7046</v>
       </c>
       <c r="F11" t="n">
-        <v>3.7185</v>
+        <v>3.7046</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7185</v>
+        <v>3.7046</v>
       </c>
       <c r="I11" t="n">
         <v>3.7358</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2879</v>
+        <v>3.2474</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7308</v>
+        <v>1.7095</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9069</v>
+        <v>0.8499</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2879</v>
+        <v>3.2474</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6307</v>
+        <v>3.5902</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3428</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6307</v>
+        <v>3.5902</v>
       </c>
       <c r="I12" t="n">
         <v>3.6816</v>
@@ -1008,7 +1008,7 @@
         <v>1.6787</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8669</v>
+        <v>0.8265</v>
       </c>
       <c r="E13" t="n">
         <v>3.1889</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0576</v>
+        <v>3.0461</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6096</v>
+        <v>1.6036</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8138</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0576</v>
+        <v>3.0461</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0576</v>
+        <v>3.0461</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0576</v>
+        <v>3.0461</v>
       </c>
       <c r="I14" t="n">
         <v>3.0718</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3782</v>
+        <v>2.3524</v>
       </c>
       <c r="C15" t="n">
-        <v>1.252</v>
+        <v>1.2384</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5394</v>
+        <v>0.4933</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3782</v>
+        <v>2.3524</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3158</v>
+        <v>2.29</v>
       </c>
       <c r="G15" t="n">
         <v>0.0624</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3158</v>
+        <v>2.29</v>
       </c>
       <c r="I15" t="n">
         <v>2.3483</v>
@@ -1136,231 +1136,231 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.202</v>
+        <v>2.2537</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1592</v>
+        <v>1.1864</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4682</v>
+        <v>0.454</v>
       </c>
       <c r="E16" t="n">
-        <v>2.202</v>
+        <v>2.2537</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6541</v>
+        <v>2.2537</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5479000000000001</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6541</v>
+        <v>2.2537</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3407</v>
+        <v>2.2727</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5479000000000001</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="L16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8886</v>
+        <v>2.2727</v>
       </c>
       <c r="N16" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9402</v>
+        <v>2.202</v>
       </c>
       <c r="C17" t="n">
-        <v>1.0214</v>
+        <v>1.1592</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3624</v>
+        <v>0.4334</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9402</v>
+        <v>2.202</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2516</v>
+        <v>1.6541</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3114</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2516</v>
+        <v>1.6541</v>
       </c>
       <c r="I17" t="n">
-        <v>1.825</v>
+        <v>1.3407</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3114</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L17" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5136</v>
+        <v>1.8886</v>
       </c>
       <c r="N17" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8594</v>
+        <v>1.9402</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9788</v>
+        <v>1.0214</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3298</v>
+        <v>0.3291</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8594</v>
+        <v>1.9402</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4615</v>
+        <v>2.2516</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3979</v>
+        <v>-0.3114</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4615</v>
+        <v>2.2516</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4615</v>
+        <v>1.825</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3979</v>
+        <v>-0.3114</v>
       </c>
       <c r="K18" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="L18" t="n">
-        <v>250</v>
+        <v>73</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8594</v>
+        <v>1.5136</v>
       </c>
       <c r="N18" t="n">
-        <v>407</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.8503</v>
+        <v>1.8612</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9741</v>
+        <v>0.9798</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3261</v>
+        <v>0.2976</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8503</v>
+        <v>1.8612</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2317</v>
+        <v>0.4633</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6186</v>
+        <v>1.3979</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2317</v>
+        <v>0.4633</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2317</v>
+        <v>0.4633</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6186</v>
+        <v>1.3979</v>
       </c>
       <c r="K19" t="n">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="L19" t="n">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="M19" t="n">
-        <v>1.8503</v>
+        <v>1.8612</v>
       </c>
       <c r="N19" t="n">
-        <v>209</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.6776</v>
+        <v>1.8503</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8831</v>
+        <v>0.9741</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2564</v>
+        <v>0.2932</v>
       </c>
       <c r="E20" t="n">
-        <v>1.6776</v>
+        <v>1.8503</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6776</v>
+        <v>1.2317</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.6186</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6776</v>
+        <v>1.2317</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6854</v>
+        <v>1.2317</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.6186</v>
       </c>
       <c r="K20" t="n">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M20" t="n">
-        <v>1.6854</v>
+        <v>1.8503</v>
       </c>
       <c r="N20" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21">
@@ -1376,7 +1376,7 @@
         <v>0.8515</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2321</v>
+        <v>0.2005</v>
       </c>
       <c r="E21" t="n">
         <v>1.6175</v>
@@ -1412,78 +1412,78 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>dexter</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3085</v>
+        <v>1.3693</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6888</v>
+        <v>0.7208</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1072</v>
+        <v>0.1016</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3085</v>
+        <v>1.3693</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3085</v>
+        <v>1.3693</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.3085</v>
+        <v>1.3693</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3085</v>
+        <v>1.3808</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>158</v>
+        <v>201</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3085</v>
+        <v>1.3808</v>
       </c>
       <c r="N22" t="n">
-        <v>158</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.189</v>
+        <v>1.3085</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6259</v>
+        <v>0.6888</v>
       </c>
       <c r="D23" t="n">
-        <v>0.059</v>
+        <v>0.0774</v>
       </c>
       <c r="E23" t="n">
-        <v>1.189</v>
+        <v>1.3085</v>
       </c>
       <c r="F23" t="n">
-        <v>1.189</v>
+        <v>1.3085</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.189</v>
+        <v>1.3085</v>
       </c>
       <c r="I23" t="n">
-        <v>1.189</v>
+        <v>1.3085</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.189</v>
+        <v>1.3085</v>
       </c>
       <c r="N23" t="n">
         <v>158</v>
@@ -1504,185 +1504,185 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.1848</v>
+        <v>1.2585</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6237</v>
+        <v>0.6625</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0573</v>
+        <v>0.0575</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1848</v>
+        <v>1.2585</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1848</v>
+        <v>1.1523</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1062</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1848</v>
+        <v>1.1523</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1848</v>
+        <v>1.1523</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1062</v>
       </c>
       <c r="K24" t="n">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1848</v>
+        <v>1.2585</v>
       </c>
       <c r="N24" t="n">
-        <v>158</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.0138</v>
+        <v>1.189</v>
       </c>
       <c r="C25" t="n">
-        <v>0.5337</v>
+        <v>0.6259</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.0118</v>
+        <v>0.0298</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0138</v>
+        <v>1.189</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0924</v>
+        <v>1.189</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0786</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.0924</v>
+        <v>1.189</v>
       </c>
       <c r="I25" t="n">
-        <v>1.0924</v>
+        <v>1.189</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0786</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="L25" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.0138</v>
+        <v>1.189</v>
       </c>
       <c r="N25" t="n">
-        <v>209</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dexter</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9301</v>
+        <v>1.1848</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4896</v>
+        <v>0.6237</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0456</v>
+        <v>0.0281</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9301</v>
+        <v>1.1848</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9301</v>
+        <v>1.1848</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9301</v>
+        <v>1.1848</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9345</v>
+        <v>1.1848</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9345</v>
+        <v>1.1848</v>
       </c>
       <c r="N26" t="n">
-        <v>201</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.859</v>
+        <v>1.0138</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4522</v>
+        <v>0.5337</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.0743</v>
+        <v>-0.04</v>
       </c>
       <c r="E27" t="n">
-        <v>0.859</v>
+        <v>1.0138</v>
       </c>
       <c r="F27" t="n">
-        <v>0.859</v>
+        <v>1.0924</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.0786</v>
       </c>
       <c r="H27" t="n">
-        <v>0.859</v>
+        <v>1.0924</v>
       </c>
       <c r="I27" t="n">
-        <v>0.863</v>
+        <v>1.0924</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.0786</v>
       </c>
       <c r="K27" t="n">
-        <v>246</v>
+        <v>132</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M27" t="n">
-        <v>0.863</v>
+        <v>1.0138</v>
       </c>
       <c r="N27" t="n">
-        <v>246</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.9782</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3913</v>
+        <v>0.515</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.121</v>
+        <v>-0.0542</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.9782</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.9782</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.9782</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.9782</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.9782</v>
       </c>
       <c r="N28" t="n">
         <v>160</v>
@@ -1734,185 +1734,185 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6997</v>
+        <v>0.8558</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3683</v>
+        <v>0.4505</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1387</v>
+        <v>-0.103</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6997</v>
+        <v>0.8558</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9754</v>
+        <v>0.8558</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2757</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9754</v>
+        <v>0.8558</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7906</v>
+        <v>0.863</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2757</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>132</v>
+        <v>246</v>
       </c>
       <c r="L29" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5148999999999999</v>
+        <v>0.863</v>
       </c>
       <c r="N29" t="n">
-        <v>205</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.7136</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3293</v>
+        <v>0.3757</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1687</v>
+        <v>-0.1596</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.7136</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.7136</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.7136</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6284</v>
+        <v>0.7136</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6284</v>
+        <v>0.7136</v>
       </c>
       <c r="N30" t="n">
-        <v>246</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5942</v>
+        <v>0.6997</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3128</v>
+        <v>0.3683</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1813</v>
+        <v>-0.1651</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5942</v>
+        <v>0.6997</v>
       </c>
       <c r="F31" t="n">
-        <v>0.488</v>
+        <v>0.9754</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1062</v>
+        <v>-0.2757</v>
       </c>
       <c r="H31" t="n">
-        <v>0.488</v>
+        <v>0.9754</v>
       </c>
       <c r="I31" t="n">
-        <v>0.488</v>
+        <v>0.7906</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1062</v>
+        <v>-0.2757</v>
       </c>
       <c r="K31" t="n">
         <v>132</v>
       </c>
       <c r="L31" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5942</v>
+        <v>0.5148999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4949</v>
+        <v>0.6232</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2605</v>
+        <v>0.3281</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2214</v>
+        <v>-0.1956</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4949</v>
+        <v>0.6232</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4949</v>
+        <v>0.6232</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4949</v>
+        <v>0.6232</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4949</v>
+        <v>0.6284</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4949</v>
+        <v>0.6284</v>
       </c>
       <c r="N32" t="n">
-        <v>160</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33">
@@ -1928,7 +1928,7 @@
         <v>0.2505</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.2291</v>
+        <v>-0.2543</v>
       </c>
       <c r="E33" t="n">
         <v>0.4759</v>
@@ -1974,7 +1974,7 @@
         <v>0.2368</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2397</v>
+        <v>-0.2647</v>
       </c>
       <c r="E34" t="n">
         <v>0.4498</v>
@@ -2020,7 +2020,7 @@
         <v>0.2276</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.2467</v>
+        <v>-0.2716</v>
       </c>
       <c r="E35" t="n">
         <v>0.4324</v>
@@ -2066,7 +2066,7 @@
         <v>0.1889</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.2764</v>
+        <v>-0.301</v>
       </c>
       <c r="E36" t="n">
         <v>0.3588</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.2884</v>
+        <v>0.2937</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1518</v>
+        <v>0.1546</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.3049</v>
+        <v>-0.3269</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2884</v>
+        <v>0.2937</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2884</v>
+        <v>0.2937</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2884</v>
+        <v>0.2937</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2884</v>
+        <v>0.2937</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.2884</v>
+        <v>0.2937</v>
       </c>
       <c r="N37" t="n">
         <v>96</v>
@@ -2158,7 +2158,7 @@
         <v>0.134</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.3185</v>
+        <v>-0.3425</v>
       </c>
       <c r="E38" t="n">
         <v>0.2545</v>
@@ -2194,81 +2194,81 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.199</v>
+        <v>0.1991</v>
       </c>
       <c r="C39" t="n">
         <v>0.1048</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.341</v>
+        <v>-0.3646</v>
       </c>
       <c r="E39" t="n">
-        <v>0.199</v>
+        <v>0.1991</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2944</v>
+        <v>0.1991</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0954</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2944</v>
+        <v>0.1991</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2386</v>
+        <v>0.1991</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.0954</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>132</v>
       </c>
       <c r="L39" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1432</v>
+        <v>0.1991</v>
       </c>
       <c r="N39" t="n">
-        <v>205</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.1127</v>
+        <v>0.199</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0593</v>
+        <v>0.1048</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3758</v>
+        <v>-0.3646</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1127</v>
+        <v>0.199</v>
       </c>
       <c r="F40" t="n">
-        <v>0.462</v>
+        <v>0.2944</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.3493</v>
+        <v>-0.0954</v>
       </c>
       <c r="H40" t="n">
-        <v>0.462</v>
+        <v>0.2944</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3745</v>
+        <v>0.2386</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3493</v>
+        <v>-0.0954</v>
       </c>
       <c r="K40" t="n">
         <v>132</v>
@@ -2277,7 +2277,7 @@
         <v>73</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0252</v>
+        <v>0.1432</v>
       </c>
       <c r="N40" t="n">
         <v>205</v>
@@ -2286,492 +2286,492 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VINI</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1095</v>
+        <v>0.1127</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0576</v>
+        <v>0.0593</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.3771</v>
+        <v>-0.399</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1095</v>
+        <v>0.1127</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1095</v>
+        <v>0.462</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.3493</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1095</v>
+        <v>0.462</v>
       </c>
       <c r="I41" t="n">
-        <v>0.11</v>
+        <v>0.3745</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.3493</v>
       </c>
       <c r="K41" t="n">
-        <v>246</v>
+        <v>132</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M41" t="n">
-        <v>0.11</v>
+        <v>0.0252</v>
       </c>
       <c r="N41" t="n">
-        <v>246</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>VINI</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0547</v>
+        <v>0.1091</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0288</v>
+        <v>0.0574</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.3993</v>
+        <v>-0.4004</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0547</v>
+        <v>0.1091</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.1749</v>
+        <v>0.1091</v>
       </c>
       <c r="G42" t="n">
-        <v>1.2296</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.1749</v>
+        <v>0.1091</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.1749</v>
+        <v>0.11</v>
       </c>
       <c r="J42" t="n">
-        <v>1.2296</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>157</v>
+        <v>246</v>
       </c>
       <c r="L42" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.05469999999999997</v>
+        <v>0.11</v>
       </c>
       <c r="N42" t="n">
-        <v>407</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.054</v>
+        <v>0.0827</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0284</v>
+        <v>0.0435</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.3995</v>
+        <v>-0.411</v>
       </c>
       <c r="E43" t="n">
-        <v>0.054</v>
+        <v>0.0827</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9902</v>
+        <v>0.0827</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.9362</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9902</v>
+        <v>0.0827</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0041</v>
+        <v>0.0834</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.9362</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="L43" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.06789999999999996</v>
+        <v>0.0834</v>
       </c>
       <c r="N43" t="n">
-        <v>468</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0413</v>
+        <v>0.0547</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0217</v>
+        <v>0.0288</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4047</v>
+        <v>-0.4221</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0413</v>
+        <v>0.0547</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0413</v>
+        <v>-1.1749</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1.2296</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0413</v>
+        <v>-1.1749</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0415</v>
+        <v>-1.1749</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1.2296</v>
       </c>
       <c r="K44" t="n">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0415</v>
+        <v>0.05469999999999997</v>
       </c>
       <c r="N44" t="n">
-        <v>201</v>
+        <v>407</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0301</v>
+        <v>0.043</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0158</v>
+        <v>0.0226</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4092</v>
+        <v>-0.4268</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0301</v>
+        <v>0.043</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2995</v>
+        <v>0.9792</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.2694</v>
+        <v>-0.9362</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2995</v>
+        <v>0.9792</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3037</v>
+        <v>1.0041</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.2694</v>
+        <v>-0.9362</v>
       </c>
       <c r="K45" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="L45" t="n">
-        <v>87</v>
+        <v>244</v>
       </c>
       <c r="M45" t="n">
-        <v>0.03430000000000005</v>
+        <v>0.06789999999999996</v>
       </c>
       <c r="N45" t="n">
-        <v>301</v>
+        <v>468</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0359</v>
+        <v>0.0267</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0189</v>
+        <v>0.0141</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.4359</v>
+        <v>-0.4333</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0359</v>
+        <v>0.0267</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0359</v>
+        <v>0.2961</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-0.2694</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0359</v>
+        <v>0.2961</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0359</v>
+        <v>0.3037</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-0.2694</v>
       </c>
       <c r="K46" t="n">
-        <v>102</v>
+        <v>214</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0359</v>
+        <v>0.03430000000000005</v>
       </c>
       <c r="N46" t="n">
-        <v>102</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.1046</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0551</v>
+        <v>-0.0051</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.4636</v>
+        <v>-0.4477</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1046</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0518</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.1564</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0518</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0518</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.1564</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L47" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1046</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>407</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.1269</v>
+        <v>-0.0359</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.0668</v>
+        <v>-0.0189</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4726</v>
+        <v>-0.4582</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1269</v>
+        <v>-0.0359</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.1269</v>
+        <v>-0.0359</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1269</v>
+        <v>-0.0359</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.1269</v>
+        <v>-0.0359</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1269</v>
+        <v>-0.0359</v>
       </c>
       <c r="N48" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.1424</v>
+        <v>-0.1046</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.075</v>
+        <v>-0.0551</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4789</v>
+        <v>-0.4856</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.1424</v>
+        <v>-0.1046</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1424</v>
+        <v>0.0518</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.1564</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1424</v>
+        <v>0.0518</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1424</v>
+        <v>0.0518</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.1564</v>
       </c>
       <c r="K49" t="n">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.1424</v>
+        <v>-0.1046</v>
       </c>
       <c r="N49" t="n">
-        <v>96</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1463</v>
+        <v>-0.1269</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.077</v>
+        <v>-0.0668</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4805</v>
+        <v>-0.4945</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1463</v>
+        <v>-0.1269</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1463</v>
+        <v>-0.1269</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1463</v>
+        <v>-0.1269</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1463</v>
+        <v>-0.1269</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1463</v>
+        <v>-0.1269</v>
       </c>
       <c r="N50" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.186</v>
+        <v>-0.1424</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0979</v>
+        <v>-0.075</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4965</v>
+        <v>-0.5006</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.186</v>
+        <v>-0.1424</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.186</v>
+        <v>-0.1424</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.186</v>
+        <v>-0.1424</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.186</v>
+        <v>-0.1424</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.186</v>
+        <v>-0.1424</v>
       </c>
       <c r="N51" t="n">
         <v>96</v>
@@ -2792,308 +2792,308 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2297</v>
+        <v>-0.1463</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1209</v>
+        <v>-0.077</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5142</v>
+        <v>-0.5022</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2297</v>
+        <v>-0.1463</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2297</v>
+        <v>-0.1463</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2297</v>
+        <v>-0.1463</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2297</v>
+        <v>-0.1463</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2297</v>
+        <v>-0.1463</v>
       </c>
       <c r="N52" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2597</v>
+        <v>-0.186</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1367</v>
+        <v>-0.0979</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5263</v>
+        <v>-0.518</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2597</v>
+        <v>-0.186</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2597</v>
+        <v>-0.186</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2597</v>
+        <v>-0.186</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2597</v>
+        <v>-0.186</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2597</v>
+        <v>-0.186</v>
       </c>
       <c r="N53" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2613</v>
+        <v>-0.2297</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1376</v>
+        <v>-0.1209</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5269</v>
+        <v>-0.5354</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2613</v>
+        <v>-0.2297</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2613</v>
+        <v>-0.2297</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2613</v>
+        <v>-0.2297</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2613</v>
+        <v>-0.2297</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2613</v>
+        <v>-0.2297</v>
       </c>
       <c r="N54" t="n">
-        <v>129</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2935</v>
+        <v>-0.2597</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1545</v>
+        <v>-0.1367</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5399</v>
+        <v>-0.5474</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2935</v>
+        <v>-0.2597</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.2935</v>
+        <v>-0.2597</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.2935</v>
+        <v>-0.2597</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2935</v>
+        <v>-0.2597</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>160</v>
+        <v>94</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2935</v>
+        <v>-0.2597</v>
       </c>
       <c r="N55" t="n">
-        <v>160</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.295</v>
+        <v>-0.2613</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1553</v>
+        <v>-0.1376</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5405</v>
+        <v>-0.548</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.295</v>
+        <v>-0.2613</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.295</v>
+        <v>-0.2613</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.295</v>
+        <v>-0.2613</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.295</v>
+        <v>-0.2613</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.295</v>
+        <v>-0.2613</v>
       </c>
       <c r="N56" t="n">
-        <v>158</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.5588</v>
+        <v>-0.295</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2942</v>
+        <v>-0.1553</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6471</v>
+        <v>-0.5614</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5588</v>
+        <v>-0.295</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.5588</v>
+        <v>-0.295</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.5588</v>
+        <v>-0.295</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.5588</v>
+        <v>-0.295</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.5588</v>
+        <v>-0.295</v>
       </c>
       <c r="N57" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.617</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3248</v>
+        <v>-0.2762</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6706</v>
+        <v>-0.653</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.617</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.617</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.617</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.617</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.617</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="N58" t="n">
         <v>132</v>
@@ -3114,78 +3114,78 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6259</v>
+        <v>-0.5588</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3295</v>
+        <v>-0.2942</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6742</v>
+        <v>-0.6665</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6259</v>
+        <v>-0.5588</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6259</v>
+        <v>-0.5588</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6259</v>
+        <v>-0.5588</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6259</v>
+        <v>-0.5588</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6259</v>
+        <v>-0.5588</v>
       </c>
       <c r="N59" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6466</v>
+        <v>-0.617</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3404</v>
+        <v>-0.3248</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6826</v>
+        <v>-0.6897</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6466</v>
+        <v>-0.617</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.6466</v>
+        <v>-0.617</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.6466</v>
+        <v>-0.617</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.6466</v>
+        <v>-0.617</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6466</v>
+        <v>-0.617</v>
       </c>
       <c r="N60" t="n">
         <v>132</v>
@@ -3206,139 +3206,139 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.665</v>
+        <v>-0.6259</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3501</v>
+        <v>-0.3295</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6933</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.665</v>
+        <v>-0.6259</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.665</v>
+        <v>-0.6259</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.665</v>
+        <v>-0.6259</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.665</v>
+        <v>-0.6259</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.665</v>
+        <v>-0.6259</v>
       </c>
       <c r="N61" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ryann</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.6793</v>
+        <v>-0.6771</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3576</v>
+        <v>-0.3564</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6958</v>
+        <v>-0.7137</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.6793</v>
+        <v>-0.6771</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.6793</v>
+        <v>-0.6771</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.6793</v>
+        <v>-0.6771</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.6793</v>
+        <v>-0.6828</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.6793</v>
+        <v>-0.6828</v>
       </c>
       <c r="N62" t="n">
-        <v>98</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>malta</t>
+          <t>ryann</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6796</v>
+        <v>-0.6793</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3578</v>
+        <v>-0.3576</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6959</v>
+        <v>-0.7145</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6796</v>
+        <v>-0.6793</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6796</v>
+        <v>-0.6793</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6796</v>
+        <v>-0.6793</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6828</v>
+        <v>-0.6793</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>201</v>
+        <v>98</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6828</v>
+        <v>-0.6793</v>
       </c>
       <c r="N63" t="n">
-        <v>201</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7037</v>
+        <v>-0.6937</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.3704</v>
+        <v>-0.3652</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7056</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7037</v>
+        <v>-0.6937</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5016</v>
       </c>
       <c r="G64" t="n">
         <v>-0.1921</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5016</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.5188</v>
+        <v>-0.5144</v>
       </c>
       <c r="J64" t="n">
         <v>-0.1921</v>
@@ -3381,7 +3381,7 @@
         <v>87</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7109000000000001</v>
+        <v>-0.7064999999999999</v>
       </c>
       <c r="N64" t="n">
         <v>301</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3753</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7094</v>
+        <v>-0.7279</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7129</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3831</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7153</v>
+        <v>-0.7338</v>
       </c>
       <c r="E66" t="n">
         <v>-0.7277</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3962</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7254</v>
+        <v>-0.7437</v>
       </c>
       <c r="E67" t="n">
         <v>-0.7526</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4031</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7307</v>
+        <v>-0.749</v>
       </c>
       <c r="E68" t="n">
         <v>-0.7658</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4494</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7662</v>
+        <v>-0.784</v>
       </c>
       <c r="E69" t="n">
         <v>-0.8536</v>
@@ -3630,7 +3630,7 @@
         <v>-0.474</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.7851</v>
+        <v>-0.8027</v>
       </c>
       <c r="E70" t="n">
         <v>-0.9005</v>
@@ -3676,7 +3676,7 @@
         <v>-0.4811</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.7906</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="E71" t="n">
         <v>-0.9139</v>
@@ -3722,7 +3722,7 @@
         <v>-0.4976</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8032</v>
+        <v>-0.8205</v>
       </c>
       <c r="E72" t="n">
         <v>-0.9453</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5616</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-0.8689</v>
       </c>
       <c r="E73" t="n">
         <v>-1.0668</v>
@@ -3804,185 +3804,185 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.2914</v>
+        <v>-1.2285</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6798</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9431</v>
+        <v>-0.9333</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.2914</v>
+        <v>-1.2285</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.2914</v>
+        <v>0.6656</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>-1.8941</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.2914</v>
+        <v>0.6656</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.2914</v>
+        <v>0.6656</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>-1.8941</v>
       </c>
       <c r="K74" t="n">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.2914</v>
+        <v>-1.2285</v>
       </c>
       <c r="N74" t="n">
-        <v>132</v>
+        <v>407</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.3439</v>
+        <v>-1.2914</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7075</v>
+        <v>-0.6798</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9643</v>
+        <v>-0.9584</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.3439</v>
+        <v>-1.2914</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3439</v>
+        <v>-1.2914</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.3439</v>
+        <v>-1.2914</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.3439</v>
+        <v>-1.2914</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.3439</v>
+        <v>-1.2914</v>
       </c>
       <c r="N75" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3674</v>
+        <v>-1.3439</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7198</v>
+        <v>-0.7075</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9738</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3674</v>
+        <v>-1.3439</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.3674</v>
+        <v>-1.3439</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.3674</v>
+        <v>-1.3439</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.3674</v>
+        <v>-1.3439</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.3674</v>
+        <v>-1.3439</v>
       </c>
       <c r="N76" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3737</v>
+        <v>-1.3674</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7232</v>
+        <v>-0.7198</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.9887</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3737</v>
+        <v>-1.3674</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5204</v>
+        <v>-1.3674</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.8941</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5204</v>
+        <v>-1.3674</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5204</v>
+        <v>-1.3674</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.8941</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="L77" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.3737</v>
+        <v>-1.3674</v>
       </c>
       <c r="N77" t="n">
-        <v>407</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78">
@@ -3998,7 +3998,7 @@
         <v>-0.7843</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0232</v>
+        <v>-1.0374</v>
       </c>
       <c r="E78" t="n">
         <v>-1.4898</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8772</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.0945</v>
+        <v>-1.1078</v>
       </c>
       <c r="E79" t="n">
         <v>-1.6663</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0244</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2075</v>
+        <v>-1.2192</v>
       </c>
       <c r="E80" t="n">
         <v>-1.946</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.3307</v>
+        <v>-2.322</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.2269</v>
+        <v>-1.2224</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.3629</v>
+        <v>-1.369</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.3307</v>
+        <v>-2.322</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.3307</v>
+        <v>-2.322</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.3307</v>
+        <v>-2.322</v>
       </c>
       <c r="I81" t="n">
         <v>-2.3415</v>
